--- a/GATEWAY/A1#111#ASPTRAPANIXX/ASPTRAPANI/FSE/1.0/ASPTP_accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#ASPTRAPANIXX/ASPTRAPANI/FSE/1.0/ASPTP_accreditamento-checklist_V8.2.7.xlsx
@@ -3055,6 +3055,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3076,9 +3079,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4565,6 +4565,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W692"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4605,14 +4606,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86" t="s">
+      <c r="B2" s="86"/>
+      <c r="C2" s="87" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="85"/>
+      <c r="D2" s="86"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -4633,14 +4634,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="93" t="s">
+      <c r="B3" s="89"/>
+      <c r="C3" s="94" t="s">
         <v>332</v>
       </c>
-      <c r="D3" s="85"/>
+      <c r="D3" s="86"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -4661,12 +4662,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="93" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="94" t="s">
         <v>334</v>
       </c>
-      <c r="D4" s="85"/>
+      <c r="D4" s="86"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -4688,12 +4689,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93" t="s">
+      <c r="A5" s="92"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="94" t="s">
         <v>335</v>
       </c>
-      <c r="D5" s="85"/>
+      <c r="D5" s="86"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4714,8 +4715,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="82"/>
-      <c r="B6" s="83"/>
+      <c r="A6" s="83"/>
+      <c r="B6" s="84"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -4850,7 +4851,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33">
         <v>4</v>
       </c>
@@ -5323,9 +5324,7 @@
       <c r="E21" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="F21" s="37">
-        <v>46085</v>
-      </c>
+      <c r="F21" s="37"/>
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
       <c r="I21" s="42"/>
@@ -5380,9 +5379,7 @@
       <c r="E22" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="F22" s="37">
-        <v>46085</v>
-      </c>
+      <c r="F22" s="37"/>
       <c r="G22" s="37"/>
       <c r="H22" s="37"/>
       <c r="I22" s="42"/>
@@ -5437,9 +5434,7 @@
       <c r="E23" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="F23" s="37">
-        <v>46085</v>
-      </c>
+      <c r="F23" s="37"/>
       <c r="G23" s="37"/>
       <c r="H23" s="37"/>
       <c r="I23" s="42"/>
@@ -5494,9 +5489,7 @@
       <c r="E24" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="F24" s="37">
-        <v>46085</v>
-      </c>
+      <c r="F24" s="37"/>
       <c r="G24" s="37"/>
       <c r="H24" s="37"/>
       <c r="I24" s="42"/>
@@ -5551,9 +5544,7 @@
       <c r="E25" s="43" t="s">
         <v>324</v>
       </c>
-      <c r="F25" s="37">
-        <v>46085</v>
-      </c>
+      <c r="F25" s="37"/>
       <c r="G25" s="37"/>
       <c r="H25" s="37"/>
       <c r="I25" s="42"/>
@@ -9984,7 +9975,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="35">
         <v>191</v>
       </c>
@@ -10027,7 +10018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="35">
         <v>376</v>
       </c>
@@ -10070,7 +10061,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="35">
         <v>417</v>
       </c>
@@ -10117,7 +10108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="35">
         <v>418</v>
       </c>
@@ -10164,7 +10155,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="35">
         <v>419</v>
       </c>
@@ -10309,9 +10300,7 @@
       <c r="E105" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="F105" s="37">
-        <v>46085</v>
-      </c>
+      <c r="F105" s="37"/>
       <c r="G105" s="37"/>
       <c r="H105" s="37"/>
       <c r="I105" s="42"/>
@@ -10960,7 +10949,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="35">
         <v>448</v>
       </c>
@@ -11007,7 +10996,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="35">
         <v>449</v>
       </c>
@@ -11051,10 +11040,10 @@
       <c r="U117" s="47"/>
       <c r="V117" s="47"/>
       <c r="W117" s="47" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="118" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="35">
         <v>450</v>
       </c>
@@ -11101,7 +11090,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="35">
         <v>451</v>
       </c>
@@ -11148,7 +11137,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="35">
         <v>452</v>
       </c>
@@ -11195,7 +11184,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="35">
         <v>454</v>
       </c>
@@ -11242,7 +11231,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="35">
         <v>455</v>
       </c>
@@ -11289,7 +11278,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="35">
         <v>460</v>
       </c>
@@ -11535,7 +11524,7 @@
       <c r="E127" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="F127" s="94">
+      <c r="F127" s="82">
         <v>46085</v>
       </c>
       <c r="G127" s="35" t="s">
@@ -11763,7 +11752,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="35">
         <v>471</v>
       </c>
@@ -11810,7 +11799,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="35">
         <v>472</v>
       </c>
@@ -15997,7 +15986,13 @@
     <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A9:W135"/>
+  <autoFilter ref="A9:W135">
+    <filterColumn colId="22">
+      <filters>
+        <filter val="KO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -18297,6 +18292,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -18440,22 +18450,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18473,30 +18492,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/A1#111#ASPTRAPANIXX/ASPTRAPANI/FSE/1.0/ASPTP_accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#ASPTRAPANIXX/ASPTRAPANI/FSE/1.0/ASPTP_accreditamento-checklist_V8.2.7.xlsx
@@ -1800,15 +1800,6 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.b454f6a15b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2026-03-04T08:34:27.942944200Z</t>
-  </si>
-  <si>
-    <t>70141a3b5dd073fa47ec726dc9a94911</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.ae13629dd8^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-04T08:34:28.848776Z</t>
   </si>
   <si>
@@ -1899,15 +1890,6 @@
     <t>2.16.840.1.113883.2.9.2.10.4.4.f0b449eaaad08e95463ac573d9fb6ff3e85677385f19f480d4de2b011fd318c4.c23b82118a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2026-03-04T08:34:35.962301600Z</t>
-  </si>
-  <si>
-    <t>08442151a5cc4ef1dc6db353c516430c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.fb2089bf75^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-04T08:34:38.136771800Z</t>
   </si>
   <si>
@@ -2007,24 +1989,6 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.5f88f520ff902e049233957cdcce37c27fb2e03fcfe90d06666477e923e6a25b.ea9f4dd26d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2026-03-04T08:34:33.515494300Z</t>
-  </si>
-  <si>
-    <t>e8a8b034bb5b13db5cfbe8dc4461c54f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.5f88f520ff902e049233957cdcce37c27fb2e03fcfe90d06666477e923e6a25b.f258c3896e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-04T08:34:33.834596600Z</t>
-  </si>
-  <si>
-    <t>2a2350c049e665b41e74fe9f3e0b35ef</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.5f88f520ff902e049233957cdcce37c27fb2e03fcfe90d06666477e923e6a25b.3faa0e744e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-04T08:34:37.607418200Z</t>
   </si>
   <si>
@@ -2320,6 +2284,42 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.120.4.4.8fe46b71d98546dc779f4a7f4859b056b254bbe56b59baa550333b2c46441c87.141bbb55af^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-09T09:01:24.618581700Z</t>
+  </si>
+  <si>
+    <t>f5acba733de8a59a984c4b4c822ad7b2</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.48c9c10c43^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-09T09:01:26.022179800Z</t>
+  </si>
+  <si>
+    <t>587f0567d0106e6666d8dc29f1f57ec5</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.5f88f520ff902e049233957cdcce37c27fb2e03fcfe90d06666477e923e6a25b.3a6afb3d1c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-09T09:01:26.338516100Z</t>
+  </si>
+  <si>
+    <t>09630998133daac41fbcae3fa160960c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.5f88f520ff902e049233957cdcce37c27fb2e03fcfe90d06666477e923e6a25b.23c0d9e1df^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-09T09:01:26.743987900Z</t>
+  </si>
+  <si>
+    <t>86c97bce6fce96f1265fb89b54694498</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.e1822450c5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4565,7 +4565,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W692"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4851,7 +4850,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33">
         <v>4</v>
       </c>
@@ -4871,13 +4870,13 @@
         <v>46085</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="J10" s="38" t="s">
         <v>58</v>
@@ -5603,13 +5602,13 @@
         <v>46085</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="I26" s="42" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="J26" s="38" t="s">
         <v>58</v>
@@ -5664,13 +5663,13 @@
         <v>46085</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="J27" s="38" t="s">
         <v>58</v>
@@ -5725,13 +5724,13 @@
         <v>46085</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="J28" s="38" t="s">
         <v>58</v>
@@ -5786,13 +5785,13 @@
         <v>46085</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="J29" s="38" t="s">
         <v>58</v>
@@ -5847,13 +5846,13 @@
         <v>46085</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="I30" s="42" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="J30" s="38" t="s">
         <v>58</v>
@@ -5908,13 +5907,13 @@
         <v>46085</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="J31" s="38" t="s">
         <v>58</v>
@@ -5969,13 +5968,13 @@
         <v>46085</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="I32" s="42" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="J32" s="38" t="s">
         <v>58</v>
@@ -6030,13 +6029,13 @@
         <v>46085</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="J33" s="38" t="s">
         <v>58</v>
@@ -6091,13 +6090,13 @@
         <v>46085</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="I34" s="42" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="J34" s="38" t="s">
         <v>58</v>
@@ -6152,13 +6151,13 @@
         <v>46085</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="J35" s="38" t="s">
         <v>58</v>
@@ -6213,13 +6212,13 @@
         <v>46085</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="J36" s="38" t="s">
         <v>58</v>
@@ -6274,13 +6273,13 @@
         <v>46085</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="J37" s="38" t="s">
         <v>58</v>
@@ -6335,13 +6334,13 @@
         <v>46085</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="I38" s="42" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="J38" s="38" t="s">
         <v>58</v>
@@ -6396,13 +6395,13 @@
         <v>46085</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="J39" s="38" t="s">
         <v>58</v>
@@ -6457,13 +6456,13 @@
         <v>46085</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="I40" s="42" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J40" s="38" t="s">
         <v>58</v>
@@ -6518,13 +6517,13 @@
         <v>46085</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="I41" s="42" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="J41" s="38" t="s">
         <v>58</v>
@@ -6579,13 +6578,13 @@
         <v>46085</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="I42" s="42" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="J42" s="38" t="s">
         <v>58</v>
@@ -6640,13 +6639,13 @@
         <v>46085</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H43" s="37" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="I43" s="42" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="J43" s="38" t="s">
         <v>58</v>
@@ -6701,13 +6700,13 @@
         <v>46085</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="I44" s="42" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="J44" s="38" t="s">
         <v>58</v>
@@ -6762,13 +6761,13 @@
         <v>46085</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="J45" s="38" t="s">
         <v>58</v>
@@ -6823,13 +6822,13 @@
         <v>46085</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="I46" s="42" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="J46" s="38" t="s">
         <v>58</v>
@@ -6884,13 +6883,13 @@
         <v>46085</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="H47" s="37" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="I47" s="42" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="J47" s="38" t="s">
         <v>58</v>
@@ -6945,13 +6944,13 @@
         <v>46085</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="I48" s="42" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="J48" s="38" t="s">
         <v>58</v>
@@ -7006,13 +7005,13 @@
         <v>46085</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="J49" s="38" t="s">
         <v>58</v>
@@ -7067,13 +7066,13 @@
         <v>46085</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="I50" s="42" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="J50" s="38" t="s">
         <v>58</v>
@@ -7128,13 +7127,13 @@
         <v>46085</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="H51" s="37" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="I51" s="42" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="J51" s="38" t="s">
         <v>58</v>
@@ -7189,13 +7188,13 @@
         <v>46085</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="I52" s="42" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="J52" s="38" t="s">
         <v>58</v>
@@ -7250,13 +7249,13 @@
         <v>46085</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="J53" s="38" t="s">
         <v>58</v>
@@ -7311,13 +7310,13 @@
         <v>46085</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="I54" s="42" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="J54" s="38" t="s">
         <v>58</v>
@@ -7372,13 +7371,13 @@
         <v>46085</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="I55" s="42" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="J55" s="38" t="s">
         <v>58</v>
@@ -7433,13 +7432,13 @@
         <v>46085</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="I56" s="42" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="J56" s="38" t="s">
         <v>58</v>
@@ -7494,13 +7493,13 @@
         <v>46085</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="H57" s="37" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="I57" s="42" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="J57" s="38" t="s">
         <v>58</v>
@@ -7555,13 +7554,13 @@
         <v>46085</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="I58" s="42" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="J58" s="38" t="s">
         <v>58</v>
@@ -7616,13 +7615,13 @@
         <v>46085</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="I59" s="42" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="J59" s="38" t="s">
         <v>58</v>
@@ -9975,7 +9974,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="35">
         <v>191</v>
       </c>
@@ -10018,7 +10017,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="35">
         <v>376</v>
       </c>
@@ -10061,7 +10060,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="35">
         <v>417</v>
       </c>
@@ -10108,7 +10107,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="35">
         <v>418</v>
       </c>
@@ -10155,7 +10154,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="35">
         <v>419</v>
       </c>
@@ -10172,16 +10171,16 @@
         <v>217</v>
       </c>
       <c r="F102" s="37">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>486</v>
+        <v>648</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>487</v>
+        <v>649</v>
       </c>
       <c r="I102" s="42" t="s">
-        <v>488</v>
+        <v>650</v>
       </c>
       <c r="J102" s="53" t="s">
         <v>58</v>
@@ -10359,13 +10358,13 @@
         <v>46085</v>
       </c>
       <c r="G106" s="37" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H106" s="37" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I106" s="42" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J106" s="60" t="s">
         <v>58</v>
@@ -10420,13 +10419,13 @@
         <v>46085</v>
       </c>
       <c r="G107" s="37" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H107" s="37" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I107" s="42" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J107" s="60" t="s">
         <v>58</v>
@@ -10481,13 +10480,13 @@
         <v>46085</v>
       </c>
       <c r="G108" s="37" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="H108" s="37" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I108" s="42" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J108" s="60" t="s">
         <v>58</v>
@@ -10542,13 +10541,13 @@
         <v>46085</v>
       </c>
       <c r="G109" s="37" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H109" s="37" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I109" s="42" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J109" s="60" t="s">
         <v>58</v>
@@ -10603,13 +10602,13 @@
         <v>46085</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="I110" s="42" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J110" s="65" t="s">
         <v>58</v>
@@ -10664,13 +10663,13 @@
         <v>46085</v>
       </c>
       <c r="G111" s="37" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H111" s="37" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I111" s="42" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J111" s="65" t="s">
         <v>58</v>
@@ -10725,13 +10724,13 @@
         <v>46085</v>
       </c>
       <c r="G112" s="37" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H112" s="37" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I112" s="42" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J112" s="70" t="s">
         <v>58</v>
@@ -10786,13 +10785,13 @@
         <v>46085</v>
       </c>
       <c r="G113" s="37" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H113" s="37" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I113" s="42" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J113" s="70" t="s">
         <v>58</v>
@@ -10847,13 +10846,13 @@
         <v>46085</v>
       </c>
       <c r="G114" s="37" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I114" s="42" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J114" s="70" t="s">
         <v>58</v>
@@ -10908,13 +10907,13 @@
         <v>46085</v>
       </c>
       <c r="G115" s="37" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="I115" s="42" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="J115" s="70" t="s">
         <v>58</v>
@@ -10949,7 +10948,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="35">
         <v>448</v>
       </c>
@@ -10996,7 +10995,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="35">
         <v>449</v>
       </c>
@@ -11043,7 +11042,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="35">
         <v>450</v>
       </c>
@@ -11060,16 +11059,16 @@
         <v>276</v>
       </c>
       <c r="F118" s="37">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>555</v>
+        <v>651</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>556</v>
+        <v>652</v>
       </c>
       <c r="I118" s="42" t="s">
-        <v>557</v>
+        <v>653</v>
       </c>
       <c r="J118" s="38" t="s">
         <v>58</v>
@@ -11090,7 +11089,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="35">
         <v>451</v>
       </c>
@@ -11107,16 +11106,16 @@
         <v>277</v>
       </c>
       <c r="F119" s="37">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>558</v>
+        <v>654</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>559</v>
+        <v>655</v>
       </c>
       <c r="I119" s="42" t="s">
-        <v>560</v>
+        <v>656</v>
       </c>
       <c r="J119" s="38" t="s">
         <v>58</v>
@@ -11137,7 +11136,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="10.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="35">
         <v>452</v>
       </c>
@@ -11157,13 +11156,13 @@
         <v>46085</v>
       </c>
       <c r="G120" s="37" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="I120" s="42" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="J120" s="38" t="s">
         <v>58</v>
@@ -11184,7 +11183,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="35">
         <v>454</v>
       </c>
@@ -11231,7 +11230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="35">
         <v>455</v>
       </c>
@@ -11278,7 +11277,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="35">
         <v>460</v>
       </c>
@@ -11295,16 +11294,16 @@
         <v>269</v>
       </c>
       <c r="F123" s="37">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>519</v>
+        <v>657</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>520</v>
+        <v>658</v>
       </c>
       <c r="I123" s="42" t="s">
-        <v>521</v>
+        <v>659</v>
       </c>
       <c r="J123" s="75" t="s">
         <v>58</v>
@@ -11406,13 +11405,13 @@
         <v>46085</v>
       </c>
       <c r="G125" s="35" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="H125" s="35" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="I125" s="35" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="J125" s="38" t="s">
         <v>58</v>
@@ -11528,13 +11527,13 @@
         <v>46085</v>
       </c>
       <c r="G127" s="35" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="H127" s="35" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="I127" s="35" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="J127" s="38" t="s">
         <v>58</v>
@@ -11589,13 +11588,13 @@
         <v>46085</v>
       </c>
       <c r="G128" s="35" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="H128" s="35" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="I128" s="35" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="J128" s="38" t="s">
         <v>58</v>
@@ -11711,13 +11710,13 @@
         <v>46085</v>
       </c>
       <c r="G130" s="35" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="H130" s="35" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="I130" s="35" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="J130" s="80" t="s">
         <v>58</v>
@@ -11752,7 +11751,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="131" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="35">
         <v>471</v>
       </c>
@@ -11772,13 +11771,13 @@
         <v>46085</v>
       </c>
       <c r="G131" s="37" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="I131" s="42" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="J131" s="38" t="s">
         <v>58</v>
@@ -11799,7 +11798,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="35">
         <v>472</v>
       </c>
@@ -11819,13 +11818,13 @@
         <v>46085</v>
       </c>
       <c r="G132" s="37" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="I132" s="42" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="J132" s="38" t="s">
         <v>58</v>
@@ -11866,13 +11865,13 @@
         <v>46085</v>
       </c>
       <c r="G133" s="37" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="I133" s="42" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="J133" s="38" t="s">
         <v>58</v>
@@ -11927,13 +11926,13 @@
         <v>46085</v>
       </c>
       <c r="G134" s="37" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="H134" s="37" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="I134" s="42" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="J134" s="38" t="s">
         <v>58</v>
@@ -15986,13 +15985,6 @@
     <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A9:W135">
-    <filterColumn colId="22">
-      <filters>
-        <filter val="KO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -18292,21 +18284,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -18450,31 +18427,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18492,6 +18460,30 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="295b7897-c886-40bf-9750-5782b814c3e4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
